--- a/bom/BOM_Three_Phase_Driver_VER2.1.xlsx
+++ b/bom/BOM_Three_Phase_Driver_VER2.1.xlsx
@@ -1,21 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28526"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EV-TECH\Desktop\Проекты\Three-Phase-80kWt\bom\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8733BB25-9836-4F53-AD17-69A03A760818}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Worksheet" sheetId="1" r:id="rId4"/>
+    <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="117">
   <si>
     <t>Reference</t>
   </si>
@@ -363,51 +368,105 @@
   </si>
   <si>
     <t>SCM3728ASA</t>
+  </si>
+  <si>
+    <t>Закуплено</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FF000000"/>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
-    <border/>
+  <borders count="2">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+  <cellXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -697,14 +756,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
-  <dimension ref="A1:G42"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H42"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="21.140625" customWidth="1"/>
+    <col min="3" max="3" width="40.7109375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -726,701 +786,858 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" t="s">
+      <c r="H1" s="4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="104.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="2">
         <v>27</v>
       </c>
-      <c r="F2" t="s">
+      <c r="E2" s="2"/>
+      <c r="F2" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" t="s">
+      <c r="G2" s="1"/>
+      <c r="H2" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="2">
         <v>25</v>
       </c>
-      <c r="F3" t="s">
+      <c r="E3" s="2"/>
+      <c r="F3" s="2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" t="s">
+      <c r="G3" s="1"/>
+      <c r="H3" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="2">
         <v>9</v>
       </c>
-      <c r="F4" t="s">
+      <c r="E4" s="2"/>
+      <c r="F4" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" t="s">
+      <c r="G4" s="1"/>
+      <c r="H4" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="2">
         <v>3</v>
       </c>
-      <c r="F5" t="s">
+      <c r="E5" s="2"/>
+      <c r="F5" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" t="s">
+      <c r="G5" s="1"/>
+      <c r="H5" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="2">
         <v>3</v>
       </c>
-      <c r="F6" t="s">
+      <c r="E6" s="2"/>
+      <c r="F6" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" t="s">
+      <c r="G6" s="1"/>
+      <c r="H6" s="1">
         <v>20</v>
       </c>
-      <c r="B7" t="s">
+    </row>
+    <row r="7" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="2">
         <v>15</v>
       </c>
-      <c r="F7" t="s">
+      <c r="E7" s="2"/>
+      <c r="F7" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" t="s">
+      <c r="G7" s="1"/>
+      <c r="H7" s="1">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="2">
         <v>1</v>
       </c>
-      <c r="F8" t="s">
+      <c r="E8" s="2"/>
+      <c r="F8" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" t="s">
+      <c r="G8" s="1"/>
+      <c r="H8" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="2">
         <v>6</v>
       </c>
-      <c r="F9" t="s">
+      <c r="E9" s="2"/>
+      <c r="F9" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" t="s">
+      <c r="G9" s="1"/>
+      <c r="H9" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="2">
         <v>6</v>
       </c>
-      <c r="F10" t="s">
+      <c r="E10" s="2"/>
+      <c r="F10" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" t="s">
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+    </row>
+    <row r="11" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="2">
         <v>3</v>
       </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" t="s">
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+    </row>
+    <row r="12" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="2">
         <v>12</v>
       </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" t="s">
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+    </row>
+    <row r="13" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="2">
         <v>6</v>
       </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" t="s">
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+    </row>
+    <row r="14" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="2">
         <v>3</v>
       </c>
-      <c r="F14" t="s">
+      <c r="E14" s="2"/>
+      <c r="F14" s="2" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15" t="s">
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+    </row>
+    <row r="15" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="2">
         <v>3</v>
       </c>
-      <c r="F15" t="s">
+      <c r="E15" s="2"/>
+      <c r="F15" s="2" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16" t="s">
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+    </row>
+    <row r="16" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="2">
         <v>3</v>
       </c>
-      <c r="F16" t="s">
+      <c r="E16" s="2"/>
+      <c r="F16" s="2" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" t="s">
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+    </row>
+    <row r="17" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="2">
         <v>3</v>
       </c>
-      <c r="F17" t="s">
+      <c r="E17" s="2"/>
+      <c r="F17" s="2" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18" t="s">
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+    </row>
+    <row r="18" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="D18">
+      <c r="D18" s="2">
         <v>6</v>
       </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19" t="s">
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+    </row>
+    <row r="19" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D19">
+      <c r="D19" s="2">
         <v>6</v>
       </c>
-      <c r="F19" t="s">
+      <c r="E19" s="2"/>
+      <c r="F19" s="2" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20" t="s">
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+    </row>
+    <row r="20" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="2">
         <v>6</v>
       </c>
-      <c r="F20" t="s">
+      <c r="E20" s="2"/>
+      <c r="F20" s="2" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21" t="s">
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+    </row>
+    <row r="21" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="D21">
+      <c r="D21" s="2">
         <v>1</v>
       </c>
-      <c r="F21" t="s">
+      <c r="E21" s="2"/>
+      <c r="F21" s="2" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22" t="s">
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+    </row>
+    <row r="22" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="D22">
+      <c r="D22" s="2">
         <v>6</v>
       </c>
-      <c r="F22" t="s">
+      <c r="E22" s="2"/>
+      <c r="F22" s="2" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23" t="s">
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+    </row>
+    <row r="23" spans="1:8" ht="195" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D23">
+      <c r="D23" s="2">
         <v>1</v>
       </c>
-      <c r="F23" t="s">
+      <c r="E23" s="2"/>
+      <c r="F23" s="2" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24" t="s">
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+    </row>
+    <row r="24" spans="1:8" ht="390" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="D24">
+      <c r="D24" s="2">
         <v>1</v>
       </c>
-      <c r="F24" t="s">
+      <c r="E24" s="2"/>
+      <c r="F24" s="2" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25" t="s">
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+    </row>
+    <row r="25" spans="1:8" ht="390" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="D25">
+      <c r="D25" s="2">
         <v>1</v>
       </c>
-      <c r="F25" t="s">
+      <c r="E25" s="2"/>
+      <c r="F25" s="2" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26" t="s">
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+    </row>
+    <row r="26" spans="1:8" ht="390" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C26" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="D26">
+      <c r="D26" s="2">
         <v>1</v>
       </c>
-      <c r="F26" t="s">
+      <c r="E26" s="2"/>
+      <c r="F26" s="2" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27" t="s">
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+    </row>
+    <row r="27" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C27" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="D27">
+      <c r="D27" s="2">
         <v>6</v>
       </c>
-      <c r="F27" t="s">
+      <c r="E27" s="2"/>
+      <c r="F27" s="2" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28" t="s">
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+    </row>
+    <row r="28" spans="1:8" ht="90" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C28" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="D28">
+      <c r="D28" s="2">
         <v>3</v>
       </c>
-      <c r="F28" t="s">
+      <c r="E28" s="2"/>
+      <c r="F28" s="2" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29" t="s">
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+    </row>
+    <row r="29" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+      <c r="A29" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="B29">
+      <c r="B29" s="2">
         <v>120</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C29" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="D29">
+      <c r="D29" s="2">
         <v>18</v>
       </c>
-      <c r="F29" t="s">
+      <c r="E29" s="2"/>
+      <c r="F29" s="2" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30" t="s">
+      <c r="G29" s="1"/>
+      <c r="H29" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A30" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="B30">
+      <c r="B30" s="2">
         <v>0</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C30" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="D30">
+      <c r="D30" s="2">
         <v>9</v>
       </c>
-      <c r="F30" t="s">
+      <c r="E30" s="2"/>
+      <c r="F30" s="2" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31" t="s">
+      <c r="G30" s="1"/>
+      <c r="H30" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="105" x14ac:dyDescent="0.25">
+      <c r="A31" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="B31">
+      <c r="B31" s="2">
         <v>10</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C31" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D31">
+      <c r="D31" s="2">
         <v>36</v>
       </c>
-      <c r="F31" t="s">
+      <c r="E31" s="2"/>
+      <c r="F31" s="2" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32" t="s">
+      <c r="G31" s="1"/>
+      <c r="H31" s="1">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+      <c r="A32" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C32" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="D32">
+      <c r="D32" s="2">
         <v>15</v>
       </c>
-      <c r="F32" t="s">
+      <c r="E32" s="2"/>
+      <c r="F32" s="2" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33" t="s">
+      <c r="G32" s="1"/>
+      <c r="H32" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A33" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C33" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="D33">
+      <c r="D33" s="2">
         <v>3</v>
       </c>
-      <c r="F33" t="s">
+      <c r="E33" s="2"/>
+      <c r="F33" s="2" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34" t="s">
+      <c r="G33" s="1"/>
+      <c r="H33" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+      <c r="A34" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C34" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="D34">
+      <c r="D34" s="2">
         <v>16</v>
       </c>
-      <c r="F34" t="s">
+      <c r="E34" s="2"/>
+      <c r="F34" s="2" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35" t="s">
+      <c r="G34" s="1"/>
+      <c r="H34" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A35" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C35" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="D35">
+      <c r="D35" s="2">
         <v>3</v>
       </c>
-      <c r="F35" t="s">
+      <c r="E35" s="2"/>
+      <c r="F35" s="2" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36" t="s">
+      <c r="G35" s="1"/>
+      <c r="H35" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A36" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C36" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="D36">
+      <c r="D36" s="2">
         <v>6</v>
       </c>
-      <c r="F36" t="s">
+      <c r="E36" s="2"/>
+      <c r="F36" s="2" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="37" spans="1:7">
-      <c r="A37" t="s">
+      <c r="G36" s="1"/>
+      <c r="H36" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A37" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C37" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="D37">
+      <c r="D37" s="2">
         <v>3</v>
       </c>
-      <c r="F37" t="s">
+      <c r="E37" s="2"/>
+      <c r="F37" s="2" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="38" spans="1:7">
-      <c r="A38" t="s">
+      <c r="G37" s="1"/>
+      <c r="H37" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A38" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="B38">
+      <c r="B38" s="2">
         <v>560</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C38" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="D38">
+      <c r="D38" s="2">
         <v>12</v>
       </c>
-      <c r="F38" t="s">
+      <c r="E38" s="2"/>
+      <c r="F38" s="2" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="39" spans="1:7">
-      <c r="A39" t="s">
+      <c r="G38" s="1"/>
+      <c r="H38" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C39" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="D39">
+      <c r="D39" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="40" spans="1:7">
-      <c r="A40" t="s">
+      <c r="E39" s="2"/>
+      <c r="F39" s="2"/>
+      <c r="G39" s="1"/>
+      <c r="H39" s="1"/>
+    </row>
+    <row r="40" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="C40" t="s">
+      <c r="C40" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="D40">
+      <c r="D40" s="2">
         <v>3</v>
       </c>
-    </row>
-    <row r="41" spans="1:7">
-      <c r="A41" t="s">
+      <c r="E40" s="2"/>
+      <c r="F40" s="2"/>
+      <c r="G40" s="1"/>
+      <c r="H40" s="1"/>
+    </row>
+    <row r="41" spans="1:8" ht="165" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="C41" t="s">
+      <c r="C41" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="D41">
+      <c r="D41" s="2">
         <v>3</v>
       </c>
-      <c r="F41" t="s">
+      <c r="E41" s="2"/>
+      <c r="F41" s="2" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="42" spans="1:7">
-      <c r="A42" t="s">
+      <c r="G41" s="1"/>
+      <c r="H41" s="1"/>
+    </row>
+    <row r="42" spans="1:8" ht="195" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="C42" t="s">
+      <c r="C42" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D42">
+      <c r="D42" s="2">
         <v>3</v>
       </c>
-      <c r="F42" t="s">
+      <c r="E42" s="2"/>
+      <c r="F42" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="G42" t="s">
+      <c r="G42" s="1" t="s">
         <v>115</v>
       </c>
+      <c r="H42" s="1"/>
     </row>
   </sheetData>
-  <sheetProtection sheet="false" objects="false" scenarios="false" formatCells="false" formatColumns="false" formatRows="false" insertColumns="false" insertRows="false" insertHyperlinks="false" deleteColumns="false" deleteRows="false" selectLockedCells="false" sort="false" autoFilter="false" pivotTables="false" selectUnlockedCells="false"/>
-  <printOptions gridLines="false" gridLinesSet="true"/>
+  <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1"/>
-  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
-    <oddHeader/>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
 </worksheet>
 </file>
--- a/bom/BOM_Three_Phase_Driver_VER2.1.xlsx
+++ b/bom/BOM_Three_Phase_Driver_VER2.1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EV-TECH\Desktop\Проекты\Three-Phase-80kWt\bom\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8733BB25-9836-4F53-AD17-69A03A760818}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{536DA2C3-67C1-4A04-9A9E-A4517CD8E633}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="115">
   <si>
     <t>Reference</t>
   </si>
@@ -115,9 +115,6 @@
     <t>D2,D3,D5,D6,D7,D8,D9,D20,D21,D22,D24,D26</t>
   </si>
   <si>
-    <t>ADM3485E</t>
-  </si>
-  <si>
     <t>Package_SO:SOIC-8_3.9x4.9mm_P1.27mm</t>
   </si>
   <si>
@@ -142,9 +139,6 @@
     <t>D12,D27,D30</t>
   </si>
   <si>
-    <t>FLT</t>
-  </si>
-  <si>
     <t>LED_SMD:LED_0805_2012Metric_Pad1.15x1.40mm_HandSolder</t>
   </si>
   <si>
@@ -154,15 +148,9 @@
     <t>D13,D28,D49</t>
   </si>
   <si>
-    <t>RDY</t>
-  </si>
-  <si>
     <t>D19,D29,D50</t>
   </si>
   <si>
-    <t>PWR</t>
-  </si>
-  <si>
     <t>D31,D32,D37,D38,D44,D64</t>
   </si>
   <si>
@@ -196,9 +184,6 @@
     <t>D51</t>
   </si>
   <si>
-    <t>+5V</t>
-  </si>
-  <si>
     <t>D58,D59,D60,D61,D62,D63</t>
   </si>
   <si>
@@ -226,9 +211,6 @@
     <t>J3</t>
   </si>
   <si>
-    <t>Control_A</t>
-  </si>
-  <si>
     <t>Connector_Molex:Molex_Micro-Fit_3.0_43045-1212_2x06_P3.00mm_Vertical</t>
   </si>
   <si>
@@ -238,15 +220,9 @@
     <t>J4</t>
   </si>
   <si>
-    <t>Control_C</t>
-  </si>
-  <si>
     <t>J5</t>
   </si>
   <si>
-    <t>Control_B</t>
-  </si>
-  <si>
     <t>L1,L2,L3,L4,L5,L6</t>
   </si>
   <si>
@@ -371,6 +347,24 @@
   </si>
   <si>
     <t>Закуплено</t>
+  </si>
+  <si>
+    <t>SN65HVD3082EDR</t>
+  </si>
+  <si>
+    <t>SCT3001WV-2x06P</t>
+  </si>
+  <si>
+    <t>NLC453232T-4R7K-PF</t>
+  </si>
+  <si>
+    <t>KP-2012SYC</t>
+  </si>
+  <si>
+    <t>KP-2012SURCK</t>
+  </si>
+  <si>
+    <t>FYLS-0805UBC</t>
   </si>
 </sst>
 </file>
@@ -391,7 +385,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -407,6 +401,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -438,7 +438,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -452,6 +452,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -787,7 +793,7 @@
         <v>6</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="104.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -987,7 +993,7 @@
       <c r="H10" s="1"/>
     </row>
     <row r="11" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="3" t="s">
         <v>27</v>
       </c>
       <c r="B11" s="2" t="s">
@@ -1002,17 +1008,19 @@
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
       <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-    </row>
-    <row r="12" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
+      <c r="H11" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
         <v>30</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>32</v>
       </c>
       <c r="D12" s="2">
         <v>12</v>
@@ -1020,17 +1028,19 @@
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
+      <c r="H12" s="1">
+        <v>40</v>
+      </c>
     </row>
     <row r="13" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="C13" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>35</v>
       </c>
       <c r="D13" s="2">
         <v>6</v>
@@ -1038,97 +1048,105 @@
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
       <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
+      <c r="H13" s="1">
+        <v>20</v>
+      </c>
     </row>
     <row r="14" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="C14" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>38</v>
       </c>
       <c r="D14" s="2">
         <v>3</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
     </row>
     <row r="15" spans="1:8" ht="75" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>41</v>
       </c>
       <c r="D15" s="2">
         <v>3</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
+      <c r="H15" s="1">
+        <v>15</v>
+      </c>
     </row>
     <row r="16" spans="1:8" ht="75" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>43</v>
+      <c r="A16" s="3" t="s">
+        <v>41</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>44</v>
+        <v>114</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D16" s="2">
         <v>3</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-    </row>
-    <row r="17" spans="1:8" ht="75" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>45</v>
-      </c>
       <c r="B17" s="2" t="s">
-        <v>46</v>
+        <v>112</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D17" s="2">
         <v>3</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
+      <c r="H17" s="1">
+        <v>15</v>
+      </c>
     </row>
     <row r="18" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
-        <v>47</v>
+      <c r="A18" s="3" t="s">
+        <v>43</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D18" s="2">
         <v>6</v>
@@ -1136,224 +1154,232 @@
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
       <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
+      <c r="H18" s="1">
+        <v>20</v>
+      </c>
     </row>
     <row r="19" spans="1:8" ht="60" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
-        <v>50</v>
+      <c r="A19" s="3" t="s">
+        <v>46</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D19" s="2">
         <v>6</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
     </row>
     <row r="20" spans="1:8" ht="60" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
-        <v>54</v>
+      <c r="A20" s="3" t="s">
+        <v>50</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D20" s="2">
         <v>6</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
+      <c r="H20" s="1">
+        <v>20</v>
+      </c>
     </row>
     <row r="21" spans="1:8" ht="75" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
-        <v>57</v>
+      <c r="A21" s="3" t="s">
+        <v>53</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>58</v>
+        <v>112</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D21" s="2">
         <v>1</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
     </row>
     <row r="22" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
-        <v>59</v>
+      <c r="A22" s="3" t="s">
+        <v>54</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D22" s="2">
         <v>6</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" s="2" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
     </row>
     <row r="23" spans="1:8" ht="195" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
-        <v>63</v>
+      <c r="A23" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="D23" s="2">
         <v>1</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" s="2" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
     </row>
     <row r="24" spans="1:8" ht="390" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
-        <v>67</v>
+      <c r="A24" s="3" t="s">
+        <v>62</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>68</v>
+        <v>110</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="D24" s="2">
         <v>1</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" s="2" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
     </row>
     <row r="25" spans="1:8" ht="390" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
-        <v>71</v>
+      <c r="A25" s="3" t="s">
+        <v>65</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>72</v>
+        <v>110</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="D25" s="2">
         <v>1</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" s="2" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="G25" s="1"/>
       <c r="H25" s="1"/>
     </row>
     <row r="26" spans="1:8" ht="390" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
-        <v>73</v>
+      <c r="A26" s="3" t="s">
+        <v>66</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="D26" s="2">
         <v>1</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" s="2" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
     </row>
-    <row r="27" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
-        <v>75</v>
+    <row r="27" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A27" s="6" t="s">
+        <v>67</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="D27" s="2">
         <v>6</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G27" s="1"/>
-      <c r="H27" s="1"/>
+        <v>70</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="H27" s="1">
+        <v>20</v>
+      </c>
     </row>
     <row r="28" spans="1:8" ht="90" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
-        <v>79</v>
+      <c r="A28" s="3" t="s">
+        <v>71</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D28" s="2">
         <v>3</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" s="2" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
     </row>
     <row r="29" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="B29" s="2">
         <v>120</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="D29" s="2">
         <v>18</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" s="2" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G29" s="1"/>
       <c r="H29" s="1">
@@ -1362,20 +1388,20 @@
     </row>
     <row r="30" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="B30" s="2">
         <v>0</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="D30" s="2">
         <v>9</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" s="2" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G30" s="1"/>
       <c r="H30" s="1">
@@ -1384,20 +1410,20 @@
     </row>
     <row r="31" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="B31" s="2">
         <v>10</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="D31" s="2">
         <v>36</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" s="2" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G31" s="1"/>
       <c r="H31" s="1">
@@ -1406,20 +1432,20 @@
     </row>
     <row r="32" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="D32" s="2">
         <v>15</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" s="2" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G32" s="1"/>
       <c r="H32" s="1">
@@ -1428,20 +1454,20 @@
     </row>
     <row r="33" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="D33" s="2">
         <v>3</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" s="2" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G33" s="1"/>
       <c r="H33" s="1">
@@ -1450,20 +1476,20 @@
     </row>
     <row r="34" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="D34" s="2">
         <v>16</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" s="2" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G34" s="1"/>
       <c r="H34" s="1">
@@ -1472,20 +1498,20 @@
     </row>
     <row r="35" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="D35" s="2">
         <v>3</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" s="2" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G35" s="1"/>
       <c r="H35" s="1">
@@ -1494,20 +1520,20 @@
     </row>
     <row r="36" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="D36" s="2">
         <v>6</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" s="2" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G36" s="1"/>
       <c r="H36" s="1">
@@ -1516,20 +1542,20 @@
     </row>
     <row r="37" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="D37" s="2">
         <v>3</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" s="2" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G37" s="1"/>
       <c r="H37" s="1">
@@ -1538,20 +1564,20 @@
     </row>
     <row r="38" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="B38" s="2">
         <v>560</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="D38" s="2">
         <v>12</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" s="2" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G38" s="1"/>
       <c r="H38" s="1">
@@ -1559,14 +1585,14 @@
       </c>
     </row>
     <row r="39" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A39" s="2" t="s">
-        <v>102</v>
+      <c r="A39" s="3" t="s">
+        <v>94</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="D39" s="2">
         <v>1</v>
@@ -1574,17 +1600,19 @@
       <c r="E39" s="2"/>
       <c r="F39" s="2"/>
       <c r="G39" s="1"/>
-      <c r="H39" s="1"/>
+      <c r="H39" s="1">
+        <v>5</v>
+      </c>
     </row>
     <row r="40" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A40" s="2" t="s">
-        <v>105</v>
+      <c r="A40" s="3" t="s">
+        <v>97</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="D40" s="2">
         <v>3</v>
@@ -1595,46 +1623,50 @@
       <c r="H40" s="1"/>
     </row>
     <row r="41" spans="1:8" ht="165" x14ac:dyDescent="0.25">
-      <c r="A41" s="2" t="s">
-        <v>108</v>
+      <c r="A41" s="3" t="s">
+        <v>100</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="D41" s="2">
         <v>3</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" s="2" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="G41" s="1"/>
-      <c r="H41" s="1"/>
+      <c r="H41" s="1">
+        <v>10</v>
+      </c>
     </row>
     <row r="42" spans="1:8" ht="195" x14ac:dyDescent="0.25">
-      <c r="A42" s="2" t="s">
-        <v>112</v>
+      <c r="A42" s="3" t="s">
+        <v>104</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D42" s="2">
         <v>3</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="G42" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="H42" s="1"/>
+        <v>106</v>
+      </c>
+      <c r="G42" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="H42" s="1">
+        <v>15</v>
+      </c>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>

--- a/bom/BOM_Three_Phase_Driver_VER2.1.xlsx
+++ b/bom/BOM_Three_Phase_Driver_VER2.1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EV-TECH\Desktop\Проекты\Three-Phase-80kWt\bom\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28A5385C-7458-44C9-A21D-52B05563F7C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F2859F5-5E73-4466-AC48-7C98C2378999}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -109,9 +109,6 @@
     <t>D4,D10,D16,D17,D18,D43</t>
   </si>
   <si>
-    <t>WRA1215S-3WR2</t>
-  </si>
-  <si>
     <t>Mornsun:WRA_S-3WR2</t>
   </si>
   <si>
@@ -362,6 +359,9 @@
   </si>
   <si>
     <t>IGBT Gate Driver</t>
+  </si>
+  <si>
+    <t>НВЦТ.EVP150-2-1.2000.150</t>
   </si>
 </sst>
 </file>
@@ -551,13 +551,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -572,13 +572,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -590,19 +589,16 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -926,13 +922,13 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="E1" s="5" t="s">
         <v>95</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>96</v>
       </c>
       <c r="F1" s="5" t="s">
         <v>2</v>
@@ -940,14 +936,14 @@
       <c r="G1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="11" t="s">
         <v>4</v>
       </c>
       <c r="I1" s="8"/>
       <c r="J1" s="2"/>
     </row>
     <row r="2" spans="1:10" ht="104.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="16" t="s">
         <v>5</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -955,8 +951,8 @@
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
-      <c r="E2" s="15" t="s">
-        <v>98</v>
+      <c r="E2" s="14" t="s">
+        <v>97</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>7</v>
@@ -969,7 +965,7 @@
       <c r="J2" s="3"/>
     </row>
     <row r="3" spans="1:10" ht="72" x14ac:dyDescent="0.3">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="16" t="s">
         <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -977,8 +973,8 @@
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
-      <c r="E3" s="15" t="s">
-        <v>98</v>
+      <c r="E3" s="14" t="s">
+        <v>97</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>10</v>
@@ -991,7 +987,7 @@
       <c r="J3" s="3"/>
     </row>
     <row r="4" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="16" t="s">
         <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -999,8 +995,8 @@
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
-      <c r="E4" s="15" t="s">
-        <v>98</v>
+      <c r="E4" s="14" t="s">
+        <v>97</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>7</v>
@@ -1013,7 +1009,7 @@
       <c r="J4" s="3"/>
     </row>
     <row r="5" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="16" t="s">
         <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
@@ -1021,8 +1017,8 @@
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
-      <c r="E5" s="15" t="s">
-        <v>98</v>
+      <c r="E5" s="14" t="s">
+        <v>97</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>7</v>
@@ -1035,7 +1031,7 @@
       <c r="J5" s="3"/>
     </row>
     <row r="6" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A6" s="18" t="s">
+      <c r="A6" s="16" t="s">
         <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
@@ -1043,8 +1039,8 @@
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
-      <c r="E6" s="15" t="s">
-        <v>98</v>
+      <c r="E6" s="14" t="s">
+        <v>97</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>7</v>
@@ -1057,7 +1053,7 @@
       <c r="J6" s="3"/>
     </row>
     <row r="7" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A7" s="18" t="s">
+      <c r="A7" s="16" t="s">
         <v>16</v>
       </c>
       <c r="B7" s="1" t="s">
@@ -1065,8 +1061,8 @@
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
-      <c r="E7" s="15" t="s">
-        <v>98</v>
+      <c r="E7" s="14" t="s">
+        <v>97</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>7</v>
@@ -1079,7 +1075,7 @@
       <c r="J7" s="3"/>
     </row>
     <row r="8" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A8" s="18" t="s">
+      <c r="A8" s="16" t="s">
         <v>18</v>
       </c>
       <c r="B8" s="1" t="s">
@@ -1087,8 +1083,8 @@
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
-      <c r="E8" s="15" t="s">
-        <v>98</v>
+      <c r="E8" s="14" t="s">
+        <v>97</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>10</v>
@@ -1101,7 +1097,7 @@
       <c r="J8" s="3"/>
     </row>
     <row r="9" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="18" t="s">
+      <c r="A9" s="16" t="s">
         <v>20</v>
       </c>
       <c r="B9" s="1" t="s">
@@ -1109,8 +1105,8 @@
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
-      <c r="E9" s="15" t="s">
-        <v>98</v>
+      <c r="E9" s="14" t="s">
+        <v>97</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>7</v>
@@ -1123,14 +1119,14 @@
       <c r="J9" s="3"/>
     </row>
     <row r="10" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A10" s="18" t="s">
+      <c r="A10" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="B10" s="11"/>
+      <c r="B10" s="10"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
-      <c r="E10" s="15" t="s">
-        <v>98</v>
+      <c r="E10" s="14" t="s">
+        <v>97</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>7</v>
@@ -1145,16 +1141,16 @@
       <c r="J10" s="3"/>
     </row>
     <row r="11" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A11" s="18" t="s">
+      <c r="A11" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="11"/>
-      <c r="C11" s="15" t="s">
+      <c r="B11" s="10"/>
+      <c r="C11" s="14" t="s">
         <v>24</v>
       </c>
       <c r="D11" s="1"/>
-      <c r="E11" s="15" t="s">
-        <v>112</v>
+      <c r="E11" s="14" t="s">
+        <v>111</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>25</v>
@@ -1167,16 +1163,16 @@
       <c r="J11" s="3"/>
     </row>
     <row r="12" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A12" s="18" t="s">
+      <c r="A12" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="B12" s="11"/>
+      <c r="B12" s="10"/>
       <c r="C12" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D12" s="1"/>
-      <c r="E12" s="15" t="s">
-        <v>111</v>
+      <c r="E12" s="14" t="s">
+        <v>110</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>27</v>
@@ -1189,19 +1185,19 @@
       <c r="J12" s="3"/>
     </row>
     <row r="13" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A13" s="18" t="s">
+      <c r="A13" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="B13" s="11"/>
+      <c r="B13" s="10"/>
       <c r="C13" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D13" s="1"/>
+      <c r="E13" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="F13" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="D13" s="1"/>
-      <c r="E13" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>30</v>
       </c>
       <c r="G13" s="1">
         <v>6</v>
@@ -1211,19 +1207,19 @@
       <c r="J13" s="3"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A14" s="18" t="s">
+      <c r="A14" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" s="10"/>
+      <c r="C14" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B14" s="11"/>
-      <c r="C14" s="1" t="s">
+      <c r="D14" s="1"/>
+      <c r="E14" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="F14" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="D14" s="1"/>
-      <c r="E14" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>33</v>
       </c>
       <c r="G14" s="1">
         <v>3</v>
@@ -1233,19 +1229,19 @@
       <c r="J14" s="3"/>
     </row>
     <row r="15" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A15" s="18" t="s">
+      <c r="A15" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="B15" s="10"/>
+      <c r="C15" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D15" s="1"/>
+      <c r="E15" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="B15" s="11"/>
-      <c r="C15" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="D15" s="1"/>
-      <c r="E15" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>35</v>
       </c>
       <c r="G15" s="1">
         <v>3</v>
@@ -1255,19 +1251,19 @@
       <c r="J15" s="3"/>
     </row>
     <row r="16" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A16" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="B16" s="11"/>
+      <c r="A16" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16" s="10"/>
       <c r="C16" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D16" s="1"/>
-      <c r="E16" s="15" t="s">
-        <v>108</v>
+      <c r="E16" s="14" t="s">
+        <v>107</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G16" s="1">
         <v>3</v>
@@ -1277,19 +1273,19 @@
       <c r="J16" s="3"/>
     </row>
     <row r="17" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A17" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="B17" s="11"/>
+      <c r="A17" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="B17" s="10"/>
       <c r="C17" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D17" s="1"/>
-      <c r="E17" s="15" t="s">
-        <v>108</v>
+      <c r="E17" s="14" t="s">
+        <v>107</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G17" s="1">
         <v>3</v>
@@ -1299,19 +1295,19 @@
       <c r="J17" s="3"/>
     </row>
     <row r="18" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A18" s="18" t="s">
+      <c r="A18" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B18" s="10"/>
+      <c r="C18" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="11"/>
-      <c r="C18" s="1" t="s">
+      <c r="D18" s="1"/>
+      <c r="E18" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="F18" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="D18" s="1"/>
-      <c r="E18" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>40</v>
       </c>
       <c r="G18" s="1">
         <v>6</v>
@@ -1321,19 +1317,19 @@
       <c r="J18" s="3"/>
     </row>
     <row r="19" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A19" s="18" t="s">
+      <c r="A19" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="10"/>
+      <c r="C19" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B19" s="11"/>
-      <c r="C19" s="1" t="s">
+      <c r="D19" s="1"/>
+      <c r="E19" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="F19" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="D19" s="1"/>
-      <c r="E19" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>43</v>
       </c>
       <c r="G19" s="1">
         <v>6</v>
@@ -1343,19 +1339,19 @@
       <c r="J19" s="3"/>
     </row>
     <row r="20" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A20" s="18" t="s">
+      <c r="A20" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" s="10"/>
+      <c r="C20" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B20" s="11"/>
-      <c r="C20" s="1" t="s">
-        <v>45</v>
-      </c>
       <c r="D20" s="1"/>
-      <c r="E20" s="15" t="s">
-        <v>106</v>
+      <c r="E20" s="14" t="s">
+        <v>105</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G20" s="1">
         <v>6</v>
@@ -1365,19 +1361,19 @@
       <c r="J20" s="3"/>
     </row>
     <row r="21" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A21" s="18" t="s">
-        <v>46</v>
-      </c>
-      <c r="B21" s="11"/>
+      <c r="A21" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="B21" s="10"/>
       <c r="C21" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D21" s="1"/>
-      <c r="E21" s="15" t="s">
-        <v>105</v>
+      <c r="E21" s="14" t="s">
+        <v>104</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G21" s="1">
         <v>1</v>
@@ -1387,19 +1383,19 @@
       <c r="J21" s="3"/>
     </row>
     <row r="22" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A22" s="18" t="s">
+      <c r="A22" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="B22" s="10"/>
+      <c r="C22" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B22" s="11"/>
-      <c r="C22" s="1" t="s">
+      <c r="D22" s="1"/>
+      <c r="E22" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="F22" s="1" t="s">
         <v>48</v>
-      </c>
-      <c r="D22" s="1"/>
-      <c r="E22" s="15" t="s">
-        <v>104</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>49</v>
       </c>
       <c r="G22" s="1">
         <v>6</v>
@@ -1409,19 +1405,19 @@
       <c r="J22" s="3"/>
     </row>
     <row r="23" spans="1:10" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="B23" s="11"/>
+      <c r="A23" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="B23" s="10"/>
       <c r="C23" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D23" s="1"/>
-      <c r="E23" s="15" t="s">
-        <v>103</v>
+      <c r="E23" s="14" t="s">
+        <v>102</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G23" s="1">
         <v>1</v>
@@ -1431,43 +1427,42 @@
       <c r="J23" s="3"/>
     </row>
     <row r="24" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A24" s="18" t="s">
+      <c r="A24" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="C24" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D24" s="10"/>
+      <c r="E24" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F24" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="D24" s="11"/>
-      <c r="E24" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>53</v>
       </c>
       <c r="G24" s="1">
         <v>6</v>
       </c>
       <c r="H24" s="6"/>
-      <c r="I24" s="10"/>
       <c r="J24" s="3"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A25" s="18" t="s">
+      <c r="A25" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="B25" s="10"/>
+      <c r="C25" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B25" s="11"/>
-      <c r="C25" s="1" t="s">
+      <c r="D25" s="1"/>
+      <c r="E25" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="F25" s="1" t="s">
         <v>56</v>
-      </c>
-      <c r="D25" s="1"/>
-      <c r="E25" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>57</v>
       </c>
       <c r="G25" s="1">
         <v>3</v>
@@ -1477,19 +1472,19 @@
       <c r="J25" s="3"/>
     </row>
     <row r="26" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A26" s="18" t="s">
-        <v>58</v>
+      <c r="A26" s="16" t="s">
+        <v>57</v>
       </c>
       <c r="B26" s="1">
         <v>120</v>
       </c>
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
-      <c r="E26" s="15" t="s">
-        <v>99</v>
+      <c r="E26" s="14" t="s">
+        <v>98</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G26" s="1">
         <v>18</v>
@@ -1499,19 +1494,19 @@
       <c r="J26" s="3"/>
     </row>
     <row r="27" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A27" s="18" t="s">
-        <v>60</v>
+      <c r="A27" s="16" t="s">
+        <v>59</v>
       </c>
       <c r="B27" s="1">
         <v>0</v>
       </c>
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
-      <c r="E27" s="15" t="s">
-        <v>99</v>
+      <c r="E27" s="14" t="s">
+        <v>98</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G27" s="1">
         <v>9</v>
@@ -1521,19 +1516,19 @@
       <c r="J27" s="3"/>
     </row>
     <row r="28" spans="1:10" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A28" s="18" t="s">
-        <v>61</v>
+      <c r="A28" s="16" t="s">
+        <v>60</v>
       </c>
       <c r="B28" s="1">
         <v>10</v>
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
-      <c r="E28" s="15" t="s">
-        <v>99</v>
+      <c r="E28" s="14" t="s">
+        <v>98</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G28" s="1">
         <v>36</v>
@@ -1543,19 +1538,19 @@
       <c r="J28" s="3"/>
     </row>
     <row r="29" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A29" s="18" t="s">
+      <c r="A29" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>63</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>64</v>
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
-      <c r="E29" s="15" t="s">
-        <v>99</v>
+      <c r="E29" s="14" t="s">
+        <v>98</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G29" s="1">
         <v>15</v>
@@ -1565,19 +1560,19 @@
       <c r="J29" s="3"/>
     </row>
     <row r="30" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A30" s="18" t="s">
+      <c r="A30" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>66</v>
       </c>
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
-      <c r="E30" s="15" t="s">
-        <v>99</v>
+      <c r="E30" s="14" t="s">
+        <v>98</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G30" s="1">
         <v>3</v>
@@ -1587,19 +1582,19 @@
       <c r="J30" s="3"/>
     </row>
     <row r="31" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A31" s="18" t="s">
+      <c r="A31" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="B31" s="1" t="s">
         <v>67</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>68</v>
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
-      <c r="E31" s="15" t="s">
-        <v>99</v>
+      <c r="E31" s="14" t="s">
+        <v>98</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G31" s="1">
         <v>16</v>
@@ -1609,19 +1604,19 @@
       <c r="J31" s="3"/>
     </row>
     <row r="32" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A32" s="18" t="s">
+      <c r="A32" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="B32" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>70</v>
       </c>
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
-      <c r="E32" s="15" t="s">
-        <v>99</v>
+      <c r="E32" s="14" t="s">
+        <v>98</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G32" s="1">
         <v>3</v>
@@ -1631,19 +1626,19 @@
       <c r="J32" s="3"/>
     </row>
     <row r="33" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A33" s="18" t="s">
+      <c r="A33" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="B33" s="1" t="s">
         <v>71</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>72</v>
       </c>
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
-      <c r="E33" s="15" t="s">
-        <v>99</v>
+      <c r="E33" s="14" t="s">
+        <v>98</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G33" s="1">
         <v>6</v>
@@ -1653,19 +1648,19 @@
       <c r="J33" s="3"/>
     </row>
     <row r="34" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A34" s="18" t="s">
+      <c r="A34" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="B34" s="1" t="s">
         <v>73</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>74</v>
       </c>
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
-      <c r="E34" s="15" t="s">
-        <v>99</v>
+      <c r="E34" s="14" t="s">
+        <v>98</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G34" s="1">
         <v>3</v>
@@ -1675,19 +1670,19 @@
       <c r="J34" s="3"/>
     </row>
     <row r="35" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A35" s="18" t="s">
-        <v>75</v>
+      <c r="A35" s="16" t="s">
+        <v>74</v>
       </c>
       <c r="B35" s="1">
         <v>560</v>
       </c>
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
-      <c r="E35" s="15" t="s">
-        <v>99</v>
+      <c r="E35" s="14" t="s">
+        <v>98</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G35" s="1">
         <v>12</v>
@@ -1697,17 +1692,17 @@
       <c r="J35" s="3"/>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A36" s="18" t="s">
+      <c r="A36" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="B36" s="10"/>
+      <c r="C36" s="1" t="s">
         <v>76</v>
-      </c>
-      <c r="B36" s="11"/>
-      <c r="C36" s="1" t="s">
-        <v>77</v>
       </c>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
       <c r="F36" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G36" s="1">
         <v>1</v>
@@ -1717,17 +1712,17 @@
       <c r="J36" s="3"/>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A37" s="18" t="s">
+      <c r="A37" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="B37" s="10"/>
+      <c r="C37" s="1" t="s">
         <v>79</v>
-      </c>
-      <c r="B37" s="11"/>
-      <c r="C37" s="1" t="s">
-        <v>80</v>
       </c>
       <c r="D37" s="1"/>
       <c r="E37" s="1"/>
       <c r="F37" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G37" s="1">
         <v>3</v>
@@ -1737,19 +1732,19 @@
       <c r="J37" s="3"/>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A38" s="18" t="s">
+      <c r="A38" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="B38" s="10"/>
+      <c r="C38" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B38" s="11"/>
-      <c r="C38" s="1" t="s">
+      <c r="D38" s="1"/>
+      <c r="E38" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="F38" s="1" t="s">
         <v>83</v>
-      </c>
-      <c r="D38" s="1"/>
-      <c r="E38" s="15" t="s">
-        <v>101</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>84</v>
       </c>
       <c r="G38" s="1">
         <v>3</v>
@@ -1759,18 +1754,18 @@
       <c r="J38" s="3"/>
     </row>
     <row r="39" spans="1:10" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="20" t="s">
+      <c r="A39" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="B39" s="12"/>
+      <c r="C39" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="D39" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="B39" s="13"/>
-      <c r="C39" s="16" t="s">
-        <v>87</v>
-      </c>
-      <c r="D39" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="E39" s="17" t="s">
-        <v>100</v>
+      <c r="E39" s="15" t="s">
+        <v>99</v>
       </c>
       <c r="F39" s="7" t="s">
         <v>27</v>
@@ -1778,8 +1773,7 @@
       <c r="G39" s="7">
         <v>3</v>
       </c>
-      <c r="H39" s="14"/>
-      <c r="I39" s="10"/>
+      <c r="H39" s="13"/>
       <c r="J39" s="3"/>
     </row>
   </sheetData>
